--- a/Acumulado_cierre_ant.xlsx
+++ b/Acumulado_cierre_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-07-01 / 2025-07-31</t>
+          <t>Ventas 2025-08-01 / 2025-08-31</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>207531.3</v>
+        <v>220153.21</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>22533</v>
+        <v>23761</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>93178.39999999999</v>
+        <v>91388.10000000001</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>11746</v>
+        <v>11106</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>32376.31</v>
+        <v>48694.01</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4077</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>120125.59</v>
+        <v>136323.38</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>15017</v>
+        <v>16537</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>50437.08</v>
+        <v>52740.65</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>6372</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>141710.59</v>
+        <v>143057.21</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>14929</v>
+        <v>14908</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>139532.92</v>
+        <v>149492.63</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>16497</v>
+        <v>17047</v>
       </c>
     </row>
   </sheetData>
